--- a/louvain_baseline_experiments/louvain_Baseline_ia-enron-only/louvain_Baseline_ia-enron-only_results.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_ia-enron-only/louvain_Baseline_ia-enron-only_results.xlsx
@@ -550,13 +550,13 @@
         <v>0.5678678995900848</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02016780000121798</v>
+        <v>0.02778069999976651</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01219920000585262</v>
+        <v>0.02372060000016063</v>
       </c>
       <c r="P2" t="n">
-        <v>0.09975580000900663</v>
+        <v>0.1334702999997717</v>
       </c>
     </row>
   </sheetData>
